--- a/data/availability/projects/palm-hills-developments/bamboo-iii.xlsx
+++ b/data/availability/projects/palm-hills-developments/bamboo-iii.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -759,7 +759,6 @@
       <c r="G2" t="n">
         <v>191</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -770,7 +769,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -816,7 +815,6 @@
       <c r="G3" t="n">
         <v>191</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -827,7 +825,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -873,7 +871,6 @@
       <c r="G4" t="n">
         <v>192</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -884,7 +881,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -930,7 +927,6 @@
       <c r="G5" t="n">
         <v>191</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -941,7 +937,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -987,7 +983,6 @@
       <c r="G6" t="n">
         <v>192</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -998,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1044,7 +1039,6 @@
       <c r="G7" t="n">
         <v>191</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1055,7 +1049,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1095,6 @@
       <c r="G8" t="n">
         <v>192</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1112,7 +1105,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1158,7 +1151,6 @@
       <c r="G9" t="n">
         <v>192</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1169,7 +1161,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1191,7 +1183,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1215,7 +1207,6 @@
       <c r="G10" t="n">
         <v>220.5</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1226,7 +1217,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1248,7 +1239,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1272,7 +1263,6 @@
       <c r="G11" t="n">
         <v>222</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1283,7 +1273,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1305,7 +1295,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1329,7 +1319,6 @@
       <c r="G12" t="n">
         <v>220.5</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1340,7 +1329,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1362,7 +1351,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1386,7 +1375,6 @@
       <c r="G13" t="n">
         <v>220.5</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1397,7 +1385,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1419,7 +1407,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1443,7 +1431,6 @@
       <c r="G14" t="n">
         <v>222</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1454,7 +1441,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1476,7 +1463,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1500,7 +1487,6 @@
       <c r="G15" t="n">
         <v>220.5</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1511,7 +1497,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1533,7 +1519,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1557,7 +1543,6 @@
       <c r="G16" t="n">
         <v>220.5</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1568,7 +1553,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1590,7 +1575,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1614,7 +1599,6 @@
       <c r="G17" t="n">
         <v>222</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1625,7 +1609,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1647,7 +1631,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1671,7 +1655,6 @@
       <c r="G18" t="n">
         <v>220.5</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1682,7 +1665,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1704,7 +1687,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1728,7 +1711,6 @@
       <c r="G19" t="n">
         <v>220.5</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1739,7 +1721,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1785,7 +1767,6 @@
       <c r="G20" t="n">
         <v>191</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1796,7 +1777,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1842,7 +1823,6 @@
       <c r="G21" t="n">
         <v>192</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1853,7 +1833,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1899,7 +1879,6 @@
       <c r="G22" t="n">
         <v>191</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1910,7 +1889,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1956,7 +1935,6 @@
       <c r="G23" t="n">
         <v>192</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1967,7 +1945,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1989,7 +1967,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2013,7 +1991,6 @@
       <c r="G24" t="n">
         <v>220.5</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2024,7 +2001,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2046,7 +2023,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2070,7 +2047,6 @@
       <c r="G25" t="n">
         <v>220.5</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2081,7 +2057,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2103,7 +2079,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2127,7 +2103,6 @@
       <c r="G26" t="n">
         <v>220.5</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2138,7 +2113,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2160,7 +2135,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2184,7 +2159,6 @@
       <c r="G27" t="n">
         <v>220.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2195,7 +2169,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2217,7 +2191,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2241,7 +2215,6 @@
       <c r="G28" t="n">
         <v>220.5</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2252,7 +2225,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2274,7 +2247,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2298,7 +2271,6 @@
       <c r="G29" t="n">
         <v>220.5</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2309,7 +2281,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2331,7 +2303,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2355,7 +2327,6 @@
       <c r="G30" t="n">
         <v>220.5</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2366,7 +2337,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2388,7 +2359,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2412,7 +2383,6 @@
       <c r="G31" t="n">
         <v>220.5</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2423,7 +2393,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2445,7 +2415,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2469,7 +2439,6 @@
       <c r="G32" t="n">
         <v>220.5</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2480,7 +2449,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2502,7 +2471,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2526,7 +2495,6 @@
       <c r="G33" t="n">
         <v>220.5</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2537,7 +2505,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2559,7 +2527,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2583,7 +2551,6 @@
       <c r="G34" t="n">
         <v>220.5</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2594,7 +2561,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2616,7 +2583,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2640,7 +2607,6 @@
       <c r="G35" t="n">
         <v>220.5</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2651,7 +2617,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2697,7 +2663,6 @@
       <c r="G36" t="n">
         <v>192</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2708,7 +2673,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2754,7 +2719,6 @@
       <c r="G37" t="n">
         <v>192</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2765,7 +2729,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2811,7 +2775,6 @@
       <c r="G38" t="n">
         <v>191</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2822,7 +2785,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2868,7 +2831,6 @@
       <c r="G39" t="n">
         <v>192</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2879,7 +2841,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2925,7 +2887,6 @@
       <c r="G40" t="n">
         <v>191</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2936,7 +2897,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2982,7 +2943,6 @@
       <c r="G41" t="n">
         <v>192</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2993,7 +2953,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3039,7 +2999,6 @@
       <c r="G42" t="n">
         <v>191</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3050,7 +3009,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3096,7 +3055,6 @@
       <c r="G43" t="n">
         <v>191</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3107,7 +3065,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3153,7 +3111,6 @@
       <c r="G44" t="n">
         <v>192</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3164,7 +3121,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
